--- a/data/trans_dic/P16A11-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,84; 17,14</t>
+          <t>11,66; 16,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,09; 22,16</t>
+          <t>16,06; 21,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 18,21</t>
+          <t>12,74; 18,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,19; 24,14</t>
+          <t>17,88; 23,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,04; 19,61</t>
+          <t>13,64; 19,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,92; 27,49</t>
+          <t>20,88; 27,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,83; 22,84</t>
+          <t>16,58; 22,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,25; 25,88</t>
+          <t>21,15; 25,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 17,49</t>
+          <t>13,62; 17,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,38; 23,87</t>
+          <t>19,39; 23,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,52; 19,58</t>
+          <t>15,59; 19,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,3; 24,14</t>
+          <t>20,46; 23,98</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,98</t>
+          <t>10,58; 14,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 17,27</t>
+          <t>12,53; 17,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,06; 16,61</t>
+          <t>12,26; 16,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 17,5</t>
+          <t>5,96; 17,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,36; 20,23</t>
+          <t>15,35; 20,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 21,43</t>
+          <t>16,19; 21,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,21; 19,36</t>
+          <t>14,6; 19,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 20,58</t>
+          <t>16,87; 20,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 16,73</t>
+          <t>13,44; 16,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,26; 18,62</t>
+          <t>15,11; 18,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,97; 17,32</t>
+          <t>13,69; 17,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 18,2</t>
+          <t>10,56; 18,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 15,34</t>
+          <t>9,86; 15,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 18,07</t>
+          <t>12,2; 17,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,38</t>
+          <t>11,75; 17,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 22,5</t>
+          <t>16,59; 22,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 19,68</t>
+          <t>14,21; 19,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 20,48</t>
+          <t>14,86; 20,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 21,74</t>
+          <t>15,76; 21,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 65,23</t>
+          <t>15,31; 70,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 16,96</t>
+          <t>13,13; 16,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,54; 18,29</t>
+          <t>14,37; 18,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,89; 18,69</t>
+          <t>14,63; 18,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,01; 55,63</t>
+          <t>17,04; 50,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 13,3</t>
+          <t>9,51; 13,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 20,99</t>
+          <t>15,83; 20,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,12; 17,74</t>
+          <t>13,14; 17,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 22,64</t>
+          <t>17,5; 22,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 18,14</t>
+          <t>13,43; 18,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 26,11</t>
+          <t>20,91; 26,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,86</t>
+          <t>14,73; 19,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,44; 25,07</t>
+          <t>18,04; 24,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 15,08</t>
+          <t>12,18; 15,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 23,02</t>
+          <t>19,03; 22,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 18,23</t>
+          <t>14,61; 17,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,76; 23,09</t>
+          <t>18,76; 22,92</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 13,9</t>
+          <t>11,58; 13,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,25; 18,04</t>
+          <t>15,4; 18,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,68; 16,1</t>
+          <t>13,69; 16,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,67; 19,62</t>
+          <t>13,55; 19,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,41; 18,08</t>
+          <t>15,54; 18,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,62; 22,32</t>
+          <t>19,56; 22,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 19,11</t>
+          <t>16,43; 19,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 39,36</t>
+          <t>19,73; 37,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,84; 15,6</t>
+          <t>13,86; 15,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 19,77</t>
+          <t>17,93; 19,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,46; 17,33</t>
+          <t>15,44; 17,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 30,12</t>
+          <t>18,35; 30,39</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82039; 118799</t>
+          <t>80783; 117626</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112889; 155450</t>
+          <t>112680; 153635</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85521; 122877</t>
+          <t>85968; 121577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115589; 153367</t>
+          <t>113607; 151244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96638; 134975</t>
+          <t>93892; 134756</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>145429; 191150</t>
+          <t>145184; 191001</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>113269; 153703</t>
+          <t>111524; 152684</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>143595; 174896</t>
+          <t>142911; 172514</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>189107; 241629</t>
+          <t>188207; 240857</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>270776; 333408</t>
+          <t>270844; 332329</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>209199; 263810</t>
+          <t>210096; 264320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>266141; 316535</t>
+          <t>268235; 314436</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101424; 144062</t>
+          <t>101804; 143151</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128172; 175818</t>
+          <t>127583; 176302</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123324; 169828</t>
+          <t>125350; 170998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89010; 208703</t>
+          <t>71036; 207918</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>148786; 195915</t>
+          <t>148682; 196997</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>168721; 220015</t>
+          <t>166220; 218332</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>148221; 201891</t>
+          <t>152272; 204864</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>161837; 197152</t>
+          <t>161621; 198462</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>259992; 322977</t>
+          <t>259513; 323739</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>311931; 380725</t>
+          <t>308861; 379155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>288576; 357730</t>
+          <t>282806; 356929</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>219535; 391463</t>
+          <t>227038; 391081</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70262; 104114</t>
+          <t>66920; 104350</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93350; 136682</t>
+          <t>92303; 133067</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91225; 131992</t>
+          <t>89224; 132240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116817; 158159</t>
+          <t>116571; 158263</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96698; 134600</t>
+          <t>97197; 136296</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>114791; 158968</t>
+          <t>115357; 158916</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>122828; 170693</t>
+          <t>123679; 171800</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>141320; 608433</t>
+          <t>142851; 653803</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>176647; 231075</t>
+          <t>178818; 229299</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222816; 280426</t>
+          <t>220334; 282006</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230017; 288705</t>
+          <t>225937; 292037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>278264; 909961</t>
+          <t>278657; 820927</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88949; 125324</t>
+          <t>89627; 128297</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149915; 198571</t>
+          <t>149704; 198213</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123011; 166298</t>
+          <t>123206; 165727</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>164444; 209811</t>
+          <t>162163; 208688</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>141071; 188440</t>
+          <t>139513; 187191</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>217023; 273855</t>
+          <t>219335; 275713</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>153145; 207290</t>
+          <t>153736; 206681</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>201303; 273606</t>
+          <t>196850; 272702</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>240637; 298693</t>
+          <t>241345; 299853</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>384730; 459106</t>
+          <t>379513; 458211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>286211; 361152</t>
+          <t>289572; 353129</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>378545; 465910</t>
+          <t>378560; 462586</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>379776; 455223</t>
+          <t>379184; 449429</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>521960; 617425</t>
+          <t>527150; 617562</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>464438; 546579</t>
+          <t>464682; 550516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472651; 678362</t>
+          <t>468711; 672069</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>520780; 611006</t>
+          <t>525033; 608714</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>695928; 791566</t>
+          <t>693845; 796944</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>582339; 677238</t>
+          <t>582402; 675898</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>724417; 1439981</t>
+          <t>721775; 1386413</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>920899; 1037997</t>
+          <t>922669; 1040186</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1243721; 1377777</t>
+          <t>1249357; 1382581</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1072519; 1202296</t>
+          <t>1071688; 1196193</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1316310; 2143246</t>
+          <t>1305539; 2162816</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A11-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,97</t>
+          <t>11,55; 16,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,06; 21,9</t>
+          <t>16,02; 21,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 18,02</t>
+          <t>12,77; 18,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,88; 23,8</t>
+          <t>17,93; 24,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,64; 19,58</t>
+          <t>14,23; 19,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,88; 27,47</t>
+          <t>20,85; 27,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,58; 22,69</t>
+          <t>16,5; 22,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,15; 25,53</t>
+          <t>20,77; 25,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,44</t>
+          <t>13,58; 17,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,39; 23,79</t>
+          <t>19,36; 24,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,59; 19,61</t>
+          <t>15,34; 19,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,46; 23,98</t>
+          <t>19,99; 23,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 14,88</t>
+          <t>10,75; 14,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,53; 17,32</t>
+          <t>12,77; 17,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 16,72</t>
+          <t>12,49; 16,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 17,43</t>
+          <t>14,55; 19,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,35; 20,34</t>
+          <t>15,15; 20,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 21,27</t>
+          <t>16,19; 21,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 19,64</t>
+          <t>14,4; 19,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,87; 20,71</t>
+          <t>16,85; 20,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,44; 16,77</t>
+          <t>13,59; 16,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 18,54</t>
+          <t>15,23; 18,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 17,28</t>
+          <t>13,91; 17,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 18,18</t>
+          <t>16,3; 19,19</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 15,38</t>
+          <t>10,33; 15,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,2; 17,59</t>
+          <t>12,19; 17,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,75; 17,41</t>
+          <t>12,16; 17,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 22,52</t>
+          <t>16,65; 22,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,21; 19,93</t>
+          <t>14,07; 19,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 20,47</t>
+          <t>14,53; 20,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,76; 21,89</t>
+          <t>15,55; 21,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,31; 70,09</t>
+          <t>14,88; 19,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,13; 16,83</t>
+          <t>13,02; 16,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,37; 18,4</t>
+          <t>14,38; 18,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,63; 18,91</t>
+          <t>14,48; 18,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,04; 50,19</t>
+          <t>16,47; 19,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,62</t>
+          <t>9,52; 13,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,83; 20,95</t>
+          <t>15,72; 21,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,14; 17,68</t>
+          <t>13,04; 17,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 22,52</t>
+          <t>16,91; 21,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,43; 18,02</t>
+          <t>13,48; 17,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 26,29</t>
+          <t>20,63; 25,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,73; 19,8</t>
+          <t>14,68; 19,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,04; 24,99</t>
+          <t>21,42; 25,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 15,14</t>
+          <t>11,96; 15,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,03; 22,97</t>
+          <t>19,27; 23,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 17,82</t>
+          <t>14,58; 17,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,76; 22,92</t>
+          <t>20,02; 23,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,58; 13,72</t>
+          <t>11,61; 13,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,4; 18,05</t>
+          <t>15,38; 18,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 16,22</t>
+          <t>13,57; 15,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,55; 19,44</t>
+          <t>17,52; 19,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,54; 18,01</t>
+          <t>15,53; 18,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,56; 22,47</t>
+          <t>19,46; 22,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 19,07</t>
+          <t>16,42; 19,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,73; 37,9</t>
+          <t>19,48; 21,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,86; 15,63</t>
+          <t>13,76; 15,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,93; 19,84</t>
+          <t>17,93; 19,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,44; 17,24</t>
+          <t>15,46; 17,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,35; 30,39</t>
+          <t>18,86; 20,43</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132854</t>
+          <t>143322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>157596</t>
+          <t>167390</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>290450</t>
+          <t>310712</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80783; 117626</t>
+          <t>80057; 115615</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112680; 153635</t>
+          <t>112381; 153263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85968; 121577</t>
+          <t>86181; 122160</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113607; 151244</t>
+          <t>123840; 165862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>93892; 134756</t>
+          <t>97975; 135167</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>145184; 191001</t>
+          <t>144947; 190358</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>111524; 152684</t>
+          <t>111022; 152802</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>142911; 172514</t>
+          <t>152286; 183315</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>188207; 240857</t>
+          <t>187547; 238766</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>270844; 332329</t>
+          <t>270497; 337085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>210096; 264320</t>
+          <t>206788; 263552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>268235; 314436</t>
+          <t>284605; 337787</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159020</t>
+          <t>173582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>179287</t>
+          <t>199794</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>373376</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101804; 143151</t>
+          <t>103371; 143938</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>127583; 176302</t>
+          <t>129951; 178327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125350; 170998</t>
+          <t>127700; 173479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71036; 207918</t>
+          <t>152567; 199824</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>148682; 196997</t>
+          <t>146751; 195729</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>166220; 218332</t>
+          <t>166184; 219012</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>152272; 204864</t>
+          <t>150173; 199319</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>161621; 198462</t>
+          <t>180461; 219846</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>259513; 323739</t>
+          <t>262271; 324090</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>308861; 379155</t>
+          <t>311470; 377596</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>282806; 356929</t>
+          <t>287211; 356009</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>227038; 391081</t>
+          <t>345498; 406754</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136621</t>
+          <t>155829</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>321718</t>
+          <t>137821</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>458340</t>
+          <t>293650</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>66920; 104350</t>
+          <t>70061; 104228</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92303; 133067</t>
+          <t>92234; 135333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>89224; 132240</t>
+          <t>92359; 131257</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116571; 158263</t>
+          <t>133358; 180272</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>97197; 136296</t>
+          <t>96206; 134398</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>115357; 158916</t>
+          <t>112803; 158020</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>123679; 171800</t>
+          <t>122099; 169485</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>142851; 653803</t>
+          <t>120737; 156231</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>178818; 229299</t>
+          <t>177408; 228993</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>220334; 282006</t>
+          <t>220408; 279955</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>225937; 292037</t>
+          <t>223678; 287735</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>278657; 820927</t>
+          <t>265707; 321762</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184843</t>
+          <t>190347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>244039</t>
+          <t>261218</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>428882</t>
+          <t>451565</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89627; 128297</t>
+          <t>89658; 126185</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149704; 198213</t>
+          <t>148724; 199748</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123206; 165727</t>
+          <t>122285; 165363</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>162163; 208688</t>
+          <t>167377; 214543</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>139513; 187191</t>
+          <t>140051; 186752</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>219335; 275713</t>
+          <t>216409; 272171</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>153736; 206681</t>
+          <t>153272; 206574</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>196850; 272702</t>
+          <t>239292; 286562</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>241345; 299853</t>
+          <t>236902; 299097</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>379513; 458211</t>
+          <t>384360; 460344</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>289572; 353129</t>
+          <t>288810; 355986</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>378560; 462586</t>
+          <t>421816; 485429</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>613339</t>
+          <t>663080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>902641</t>
+          <t>766222</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1515979</t>
+          <t>1429302</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>379184; 449429</t>
+          <t>380247; 452546</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>527150; 617562</t>
+          <t>526209; 616452</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>464682; 550516</t>
+          <t>460657; 542765</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>468711; 672069</t>
+          <t>618741; 705213</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>525033; 608714</t>
+          <t>524789; 611644</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>693845; 796944</t>
+          <t>690133; 794399</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>582402; 675898</t>
+          <t>581873; 681888</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>721775; 1386413</t>
+          <t>726964; 803573</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>922669; 1040186</t>
+          <t>915783; 1028937</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1249357; 1382581</t>
+          <t>1249622; 1381315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1071688; 1196193</t>
+          <t>1072991; 1201570</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1305539; 2162816</t>
+          <t>1369921; 1483872</t>
         </is>
       </c>
     </row>
